--- a/sys_val.xlsx
+++ b/sys_val.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Prj\Power-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E65861-4960-4CBA-85E5-4C23B56D5D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF353E6B-10D7-47E8-8A2C-FF8E3D47612D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" tabRatio="935"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="205" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="203" uniqueCount="92">
   <si>
     <t>Gauss Seidel (GS)</t>
   </si>
@@ -218,106 +218,103 @@
     <t>BUS10</t>
   </si>
   <si>
+    <t>SLACK</t>
+  </si>
+  <si>
+    <t>R_a_pu</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>X_prime_d_pu</t>
+  </si>
+  <si>
+    <t>PV</t>
+  </si>
+  <si>
+    <t>LINE01</t>
+  </si>
+  <si>
+    <t>LINE02</t>
+  </si>
+  <si>
+    <t>LINE03</t>
+  </si>
+  <si>
+    <t>LINE04</t>
+  </si>
+  <si>
+    <t>LINE05</t>
+  </si>
+  <si>
+    <t>LINE06</t>
+  </si>
+  <si>
+    <t>LINE07</t>
+  </si>
+  <si>
+    <t>LINE08</t>
+  </si>
+  <si>
+    <t>LINE09</t>
+  </si>
+  <si>
+    <t>LINE10</t>
+  </si>
+  <si>
+    <t>LINE11</t>
+  </si>
+  <si>
+    <t>PQ</t>
+  </si>
+  <si>
+    <t>TRX01</t>
+  </si>
+  <si>
+    <t>TRX02</t>
+  </si>
+  <si>
+    <t>TRX03</t>
+  </si>
+  <si>
+    <t>methods_to_apply</t>
+  </si>
+  <si>
+    <t>run_Y_or_N</t>
+  </si>
+  <si>
+    <t>values</t>
+  </si>
+  <si>
+    <t>0.00000000001</t>
+  </si>
+  <si>
+    <t>1000000</t>
+  </si>
+  <si>
+    <t>general_settings</t>
+  </si>
+  <si>
+    <t>angular_transient_stability_settings</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>BUS11</t>
   </si>
   <si>
-    <t>SLACK</t>
-  </si>
-  <si>
-    <t>R_a_pu</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>X_prime_d_pu</t>
-  </si>
-  <si>
-    <t>PV</t>
-  </si>
-  <si>
-    <t>LINE01</t>
-  </si>
-  <si>
-    <t>LINE02</t>
-  </si>
-  <si>
-    <t>LINE03</t>
-  </si>
-  <si>
-    <t>LINE04</t>
-  </si>
-  <si>
-    <t>LINE05</t>
-  </si>
-  <si>
-    <t>LINE06</t>
-  </si>
-  <si>
-    <t>LINE07</t>
-  </si>
-  <si>
-    <t>LINE08</t>
-  </si>
-  <si>
-    <t>LINE09</t>
-  </si>
-  <si>
-    <t>LINE10</t>
-  </si>
-  <si>
-    <t>LINE11</t>
-  </si>
-  <si>
-    <t>PQ</t>
-  </si>
-  <si>
-    <t>TRX01</t>
-  </si>
-  <si>
-    <t>TRX02</t>
-  </si>
-  <si>
-    <t>TRX03</t>
-  </si>
-  <si>
-    <t>methods_to_apply</t>
-  </si>
-  <si>
-    <t>run_Y_or_N</t>
-  </si>
-  <si>
-    <t>values</t>
-  </si>
-  <si>
-    <t>0.00000000001</t>
-  </si>
-  <si>
-    <t>1000000</t>
-  </si>
-  <si>
-    <t>general_settings</t>
-  </si>
-  <si>
-    <t>angular_transient_stability_settings</t>
-  </si>
-  <si>
-    <t>result_1</t>
-  </si>
-  <si>
-    <t>result_2</t>
-  </si>
-  <si>
-    <t>result_3</t>
-  </si>
-  <si>
-    <t>result_4</t>
-  </si>
-  <si>
-    <t>result_5</t>
-  </si>
-  <si>
-    <t>result_6</t>
+    <t>sol_10</t>
+  </si>
+  <si>
+    <t>sol_11</t>
+  </si>
+  <si>
+    <t>sol_12</t>
+  </si>
+  <si>
+    <t>sol_13</t>
   </si>
 </sst>
 </file>
@@ -696,22 +693,22 @@
   <sheetData>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>81</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.3">
@@ -719,7 +716,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>0</v>
@@ -739,7 +736,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>1</v>
@@ -751,7 +748,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
@@ -759,7 +756,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>2</v>
@@ -771,7 +768,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.3">
@@ -779,7 +776,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>3</v>
@@ -1154,13 +1151,13 @@
         <v>15</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>14</v>
@@ -1210,7 +1207,7 @@
         <v>0.2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2" s="6">
         <v>1.04</v>
@@ -1257,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G3" s="6">
         <v>1</v>
@@ -1304,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G4" s="6">
         <v>1</v>
@@ -1351,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G5" s="6">
         <v>1</v>
@@ -1398,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G6" s="6">
         <v>1</v>
@@ -1445,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G7" s="6">
         <v>1</v>
@@ -1492,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G8" s="6">
         <v>1</v>
@@ -1539,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G9" s="6">
         <v>1</v>
@@ -1586,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G10" s="6">
         <v>1</v>
@@ -1633,7 +1630,7 @@
         <v>0.15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G11" s="6">
         <v>1.0349999999999999</v>
@@ -1665,7 +1662,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="B12" s="8">
         <v>11</v>
@@ -1680,7 +1677,7 @@
         <v>0.25</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G12" s="6">
         <v>1.03</v>
@@ -1753,7 +1750,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2" s="8">
         <v>2</v>
@@ -1773,7 +1770,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" s="8">
         <v>2</v>
@@ -1793,7 +1790,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4" s="8">
         <v>2</v>
@@ -1813,7 +1810,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" s="8">
         <v>3</v>
@@ -1833,7 +1830,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6" s="8">
         <v>3</v>
@@ -1853,7 +1850,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7" s="8">
         <v>4</v>
@@ -1873,7 +1870,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8" s="8">
         <v>4</v>
@@ -1893,7 +1890,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="8">
         <v>5</v>
@@ -1913,7 +1910,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10" s="8">
         <v>6</v>
@@ -1933,7 +1930,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B11" s="8">
         <v>7</v>
@@ -1953,7 +1950,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12" s="8">
         <v>8</v>
@@ -2005,7 +2002,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B2" s="8">
         <v>1</v>
@@ -2022,7 +2019,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3" s="8">
         <v>4</v>
@@ -2039,7 +2036,7 @@
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" s="8">
         <v>7</v>
